--- a/diseases/d002/2026-2029.xlsx
+++ b/diseases/d002/2026-2029.xlsx
@@ -15830,6 +15830,154 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr"/>
+      <c r="AT101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15863,7 +16011,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -15946,7 +16094,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10">
@@ -15956,7 +16104,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d002/2026-2029.xlsx
+++ b/diseases/d002/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1454,9 +1451,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1602,9 +1596,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -3230,9 +3221,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3771,9 +3759,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -3919,9 +3904,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -5399,9 +5381,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5940,9 +5919,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -6088,9 +6064,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -7420,9 +7393,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -7568,9 +7538,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8109,9 +8076,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -8257,9 +8221,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -9589,9 +9550,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -9737,9 +9695,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10278,9 +10233,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -10426,9 +10378,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -12054,9 +12003,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -12350,9 +12296,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -12498,9 +12441,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -12646,9 +12586,6 @@
       <c r="O79" t="n">
         <v>2</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.008691384892873792</v>
       </c>
@@ -12794,9 +12731,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -12942,9 +12876,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -13090,9 +13021,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -13238,9 +13166,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -13386,9 +13311,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -13534,9 +13456,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -13682,9 +13601,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -13830,9 +13746,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -13978,9 +13891,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -14126,9 +14036,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -14274,9 +14181,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -14422,9 +14326,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -14570,9 +14471,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -14718,9 +14616,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -14866,9 +14761,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -15014,9 +14906,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -15162,9 +15051,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -15310,9 +15196,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -15458,9 +15341,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -15606,9 +15486,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -15754,9 +15631,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -15900,9 +15774,6 @@
         <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" t="n">
         <v>0</v>
       </c>
       <c r="R101" t="n">

--- a/diseases/d002/2026-2029.xlsx
+++ b/diseases/d002/2026-2029.xlsx
@@ -12104,12 +12104,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -12148,79 +12148,87 @@
       <c r="O76" t="n">
         <v>1</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7.077571156938746e-05</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CHOLERA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CHOLERA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12247,17 +12255,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -12291,81 +12299,170 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CHOLERA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CHOLERA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary cholera notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN77" t="b">
+        <v>1</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CHOLERA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -12397,12 +12494,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -12436,13 +12533,16 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>7.077571156938746e-05</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -12475,42 +12575,42 @@
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -12542,12 +12642,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -12581,13 +12681,13 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>0.008691384892873792</v>
+        <v>0</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -12620,17 +12720,17 @@
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -12640,17 +12740,17 @@
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
@@ -12687,12 +12787,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -12717,7 +12817,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -12765,42 +12865,42 @@
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -12832,12 +12932,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -12862,7 +12962,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -12871,13 +12971,13 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -12910,42 +13010,42 @@
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13007,7 +13107,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -13152,7 +13252,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -13297,7 +13397,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -13442,7 +13542,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -13587,7 +13687,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -13732,7 +13832,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -13847,12 +13947,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -13877,12 +13977,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N88" t="n">
@@ -13925,42 +14025,42 @@
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -13992,12 +14092,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -14022,12 +14122,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N89" t="n">
@@ -14070,42 +14170,42 @@
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -14137,12 +14237,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -14167,7 +14267,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -14215,42 +14315,42 @@
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14282,12 +14382,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -14312,7 +14412,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -14360,42 +14460,42 @@
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -14457,7 +14557,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -14602,7 +14702,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -14747,7 +14847,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -14892,7 +14992,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -15037,7 +15137,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -15182,7 +15282,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -15327,7 +15427,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -15442,12 +15542,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -15472,12 +15572,12 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N99" t="n">
@@ -15520,42 +15620,42 @@
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -15587,12 +15687,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -15617,12 +15717,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N100" t="n">
@@ -15665,42 +15765,42 @@
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15732,12 +15832,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -15762,7 +15862,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -15810,40 +15910,330 @@
       </c>
       <c r="AV101" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr"/>
+      <c r="AT102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr"/>
+      <c r="AT103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW101" t="inlineStr">
+      <c r="AW103" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
+      <c r="AX103" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY101" t="inlineStr">
+      <c r="AY103" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
+      <c r="AZ103" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA101" t="inlineStr">
+      <c r="BA103" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB101" t="inlineStr">
+      <c r="BB103" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC101" t="inlineStr">
+      <c r="BC103" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -15965,7 +16355,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10">
@@ -15975,7 +16365,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11">
@@ -15995,7 +16385,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -16027,7 +16417,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d002/2026-2029.xlsx
+++ b/diseases/d002/2026-2029.xlsx
@@ -16239,6 +16239,151 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr"/>
+      <c r="AT104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16272,7 +16417,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -16355,7 +16500,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10">
@@ -16365,7 +16510,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d002/2026-2029.xlsx
+++ b/diseases/d002/2026-2029.xlsx
@@ -14382,12 +14382,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -14421,13 +14421,16 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O91" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>0.0002831028462775499</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -14460,42 +14463,42 @@
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -14527,12 +14530,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -14557,7 +14560,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -14605,42 +14608,42 @@
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -14672,12 +14675,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -14750,42 +14753,42 @@
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -14817,12 +14820,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -14847,7 +14850,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -14895,42 +14898,42 @@
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -14962,12 +14965,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -15040,42 +15043,42 @@
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15107,12 +15110,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -15137,7 +15140,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -15185,42 +15188,42 @@
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -15252,12 +15255,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -15330,42 +15333,42 @@
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15397,12 +15400,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -15427,7 +15430,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -15475,42 +15478,42 @@
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -15542,12 +15545,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -15620,42 +15623,42 @@
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15687,12 +15690,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -15717,7 +15720,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -15765,42 +15768,42 @@
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -15832,12 +15835,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -15862,12 +15865,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N101" t="n">
@@ -15910,42 +15913,42 @@
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -15977,12 +15980,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -16055,42 +16058,42 @@
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16122,12 +16125,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -16152,7 +16155,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -16200,42 +16203,42 @@
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -16297,7 +16300,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -16379,6 +16382,151 @@
         </is>
       </c>
       <c r="BC104" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr"/>
+      <c r="AT105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -16500,7 +16648,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10">
@@ -16510,7 +16658,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11">
@@ -16562,7 +16710,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d002/2026-2029.xlsx
+++ b/diseases/d002/2026-2029.xlsx
@@ -16532,6 +16532,151 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr"/>
+      <c r="AT106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16565,7 +16710,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -16648,7 +16793,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10">
@@ -16658,7 +16803,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d002/2026-2029.xlsx
+++ b/diseases/d002/2026-2029.xlsx
@@ -24774,12 +24774,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24852,42 +24852,42 @@
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -24919,12 +24919,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -24997,42 +24997,42 @@
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -25064,12 +25064,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -25142,42 +25142,42 @@
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25209,12 +25209,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -25239,7 +25239,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -25253,9 +25253,6 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
-      <c r="P147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
@@ -25264,77 +25261,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA147" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ147" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS147" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25361,7 +25349,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -25413,98 +25401,18 @@
       <c r="P148" t="n">
         <v>0</v>
       </c>
-      <c r="U148" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V148" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W148" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X148" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R148" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD148" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE148" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF148" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG148" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH148" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI148" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM148" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN148" t="b">
-        <v>1</v>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
@@ -25598,17 +25506,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -25633,7 +25541,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -25647,76 +25555,168 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
-      <c r="R149" t="n">
-        <v>0</v>
-      </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN149" t="b">
+        <v>1</v>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS149" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -25748,12 +25748,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -25826,42 +25826,42 @@
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25893,12 +25893,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -25923,7 +25923,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -25937,9 +25937,6 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
-      <c r="P151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
@@ -25948,77 +25945,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA151" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ151" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26045,7 +26033,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -26097,98 +26085,18 @@
       <c r="P152" t="n">
         <v>0</v>
       </c>
-      <c r="U152" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V152" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W152" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X152" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y152" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R152" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD152" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE152" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF152" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG152" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH152" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI152" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN152" t="b">
-        <v>1</v>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
@@ -26282,17 +26190,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -26317,7 +26225,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -26331,76 +26239,168 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
-      <c r="R153" t="n">
-        <v>0</v>
-      </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM153" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN153" t="b">
+        <v>1</v>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR153" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS153" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -26432,12 +26432,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -26510,42 +26510,42 @@
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26577,12 +26577,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -26607,7 +26607,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -26621,9 +26621,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="P155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -26632,77 +26629,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA155" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ155" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS155" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26729,7 +26717,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -26781,98 +26769,18 @@
       <c r="P156" t="n">
         <v>0</v>
       </c>
-      <c r="U156" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V156" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X156" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y156" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD156" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE156" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF156" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG156" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN156" t="b">
-        <v>1</v>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
@@ -26966,17 +26874,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -27001,7 +26909,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -27015,76 +26923,168 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="R157" t="n">
-        <v>0</v>
-      </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN157" t="b">
+        <v>1</v>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -27116,12 +27116,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -27194,42 +27194,42 @@
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27261,12 +27261,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -27291,7 +27291,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -27339,42 +27339,42 @@
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27406,12 +27406,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -27450,9 +27450,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="P160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -27461,77 +27458,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA160" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ160" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27558,7 +27546,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -27610,98 +27598,18 @@
       <c r="P161" t="n">
         <v>0</v>
       </c>
-      <c r="U161" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V161" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W161" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X161" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y161" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD161" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE161" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF161" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG161" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH161" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI161" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM161" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN161" t="b">
-        <v>1</v>
       </c>
       <c r="AO161" t="inlineStr">
         <is>
@@ -27795,17 +27703,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -27830,12 +27738,12 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N162" t="n">
@@ -27844,76 +27752,168 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="R162" t="n">
-        <v>0</v>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN162" t="b">
+        <v>1</v>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -27945,12 +27945,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -28023,42 +28023,42 @@
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -28090,12 +28090,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -28120,7 +28120,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -28168,42 +28168,42 @@
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -28235,12 +28235,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -28279,9 +28279,6 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
-      <c r="P165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0</v>
       </c>
@@ -28290,77 +28287,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA165" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ165" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28387,7 +28375,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -28439,98 +28427,18 @@
       <c r="P166" t="n">
         <v>0</v>
       </c>
-      <c r="U166" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V166" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W166" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X166" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y166" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R166" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD166" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE166" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF166" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG166" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI166" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ166" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM166" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN166" t="b">
-        <v>1</v>
       </c>
       <c r="AO166" t="inlineStr">
         <is>
@@ -28624,17 +28532,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -28659,7 +28567,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -28673,76 +28581,168 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="R167" t="n">
-        <v>0</v>
-      </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN167" t="b">
+        <v>1</v>
       </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -28774,12 +28774,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -28818,9 +28818,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="P168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -28829,77 +28826,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA168" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ168" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS168" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28926,7 +28914,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -28978,98 +28966,18 @@
       <c r="P169" t="n">
         <v>0</v>
       </c>
-      <c r="U169" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V169" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W169" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X169" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y169" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R169" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD169" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE169" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF169" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG169" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH169" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI169" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN169" t="b">
-        <v>1</v>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
@@ -29163,17 +29071,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -29198,7 +29106,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -29212,76 +29120,168 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="R170" t="n">
-        <v>0</v>
-      </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN170" t="b">
+        <v>1</v>
       </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
       <c r="AT170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -29313,12 +29313,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -29357,9 +29357,6 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
-      <c r="P171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0</v>
       </c>
@@ -29368,77 +29365,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA171" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ171" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS171" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29465,7 +29453,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -29517,98 +29505,18 @@
       <c r="P172" t="n">
         <v>0</v>
       </c>
-      <c r="U172" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="V172" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_CHOLERA</t>
-        </is>
-      </c>
-      <c r="W172" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X172" t="inlineStr">
-        <is>
-          <t>Cholera</t>
-        </is>
-      </c>
-      <c r="Y172" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R172" t="n">
+        <v>0</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD172" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE172" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF172" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG172" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH172" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI172" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ172" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK172" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM172" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN172" t="b">
-        <v>1</v>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
@@ -29674,6 +29582,243 @@
         </is>
       </c>
       <c r="BC172" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>cholera</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>霍乱</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" t="n">
+        <v>0</v>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>Cholera</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN173" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_CHOLERA; SER_SG_HIST_CHOLERA</t>
+        </is>
+      </c>
+      <c r="AT173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV173" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA173" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC173" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -29795,7 +29940,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10">
@@ -29805,7 +29950,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
